--- a/ksoft_old/docs/records/Accounts_Numbers.xlsx
+++ b/ksoft_old/docs/records/Accounts_Numbers.xlsx
@@ -31092,13 +31092,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E34B7146-9BF6-4CC9-8F5F-6BD5145D81DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDD97F43-C926-4A9F-B72B-7F0924D21CBE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E409D18-0F46-4617-9914-7EEA772BB3E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32B80EC-CF67-403B-A83F-6CB1391B7774}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6EB893B-55DF-417A-B3B0-0D743AA99C57}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7D58577-813A-4B1C-A6C2-460FFE6941E8}"/>
 </file>
--- a/ksoft_old/docs/records/Accounts_Numbers.xlsx
+++ b/ksoft_old/docs/records/Accounts_Numbers.xlsx
@@ -31092,13 +31092,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDD97F43-C926-4A9F-B72B-7F0924D21CBE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03A4D6D7-BE36-46DA-9324-F10A41DB872B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32B80EC-CF67-403B-A83F-6CB1391B7774}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1EEE20D-ABAF-45FC-B9CB-87DEC49B7ACD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7D58577-813A-4B1C-A6C2-460FFE6941E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{021EC41D-95A3-43CA-9015-F8F71DAB2FE9}"/>
 </file>
--- a/ksoft_old/docs/records/Accounts_Numbers.xlsx
+++ b/ksoft_old/docs/records/Accounts_Numbers.xlsx
@@ -31092,13 +31092,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03A4D6D7-BE36-46DA-9324-F10A41DB872B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E34B7146-9BF6-4CC9-8F5F-6BD5145D81DD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1EEE20D-ABAF-45FC-B9CB-87DEC49B7ACD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E409D18-0F46-4617-9914-7EEA772BB3E8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{021EC41D-95A3-43CA-9015-F8F71DAB2FE9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6EB893B-55DF-417A-B3B0-0D743AA99C57}"/>
 </file>